--- a/設計書/02.テーブル設計書/テーブル設計書.xlsx
+++ b/設計書/02.テーブル設計書/テーブル設計書.xlsx
@@ -5,11 +5,11 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yu-fujii\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yu-fujii\Desktop\設計書\設計書\02.テーブル設計書\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9384" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9384"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="74">
   <si>
     <t>テーブル定義書</t>
     <rPh sb="4" eb="7">
@@ -450,6 +450,29 @@
   </si>
   <si>
     <t>act_team_list</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>employee_gender</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>性別</t>
+    <rPh sb="0" eb="2">
+      <t>セイベツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VARCHAR</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>employee_notes</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VARCHAR</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1870,7 +1893,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:K21"/>
+  <dimension ref="A1:K23"/>
   <sheetFormatPr defaultRowHeight="16.2" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.21875" customWidth="1"/>
@@ -2030,7 +2053,7 @@
     </row>
     <row r="7" spans="1:11" ht="16.2" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="10">
-        <f t="shared" ref="A7:A21" si="0">ROW()-5</f>
+        <f t="shared" ref="A7:A23" si="0">ROW()-5</f>
         <v>2</v>
       </c>
       <c r="B7" s="10"/>
@@ -2194,7 +2217,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="16.2" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="10">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -2202,13 +2225,13 @@
       <c r="B13" s="10"/>
       <c r="C13" s="10"/>
       <c r="D13" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="E13" s="10" t="s">
-        <v>28</v>
+        <v>69</v>
+      </c>
+      <c r="E13" s="13" t="s">
+        <v>70</v>
       </c>
       <c r="F13" s="10" t="s">
-        <v>48</v>
+        <v>71</v>
       </c>
       <c r="G13" s="10">
         <v>1</v>
@@ -2216,15 +2239,13 @@
       <c r="H13" s="10">
         <v>1</v>
       </c>
-      <c r="I13" s="10" t="s">
-        <v>33</v>
-      </c>
+      <c r="I13" s="10"/>
       <c r="J13" s="10"/>
       <c r="K13" s="10" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" ht="16.2" customHeight="1" x14ac:dyDescent="0.2">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="10">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -2232,25 +2253,23 @@
       <c r="B14" s="10"/>
       <c r="C14" s="10"/>
       <c r="D14" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="E14" s="10" t="s">
-        <v>7</v>
+        <v>72</v>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>15</v>
       </c>
       <c r="F14" s="10" t="s">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="G14" s="10">
-        <v>8</v>
-      </c>
-      <c r="H14" s="10"/>
-      <c r="I14" s="10" t="s">
-        <v>33</v>
-      </c>
+        <v>6000</v>
+      </c>
+      <c r="H14" s="10">
+        <v>2000</v>
+      </c>
+      <c r="I14" s="10"/>
       <c r="J14" s="10"/>
-      <c r="K14" s="10" t="s">
-        <v>40</v>
-      </c>
+      <c r="K14" s="10"/>
     </row>
     <row r="15" spans="1:11" ht="16.2" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="10">
@@ -2260,24 +2279,26 @@
       <c r="B15" s="10"/>
       <c r="C15" s="10"/>
       <c r="D15" s="10" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E15" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="F15" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="G15" s="10">
         <v>1</v>
       </c>
-      <c r="F15" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="G15" s="10">
-        <v>8</v>
-      </c>
-      <c r="H15" s="10"/>
+      <c r="H15" s="10">
+        <v>1</v>
+      </c>
       <c r="I15" s="10" t="s">
         <v>33</v>
       </c>
       <c r="J15" s="10"/>
       <c r="K15" s="10" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="16.2" customHeight="1" x14ac:dyDescent="0.2">
@@ -2287,14 +2308,26 @@
       </c>
       <c r="B16" s="10"/>
       <c r="C16" s="10"/>
-      <c r="D16" s="10"/>
-      <c r="E16" s="10"/>
-      <c r="F16" s="10"/>
-      <c r="G16" s="10"/>
+      <c r="D16" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="E16" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="F16" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="G16" s="10">
+        <v>8</v>
+      </c>
       <c r="H16" s="10"/>
-      <c r="I16" s="10"/>
+      <c r="I16" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="J16" s="10"/>
-      <c r="K16" s="10"/>
+      <c r="K16" s="10" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="17" spans="1:11" ht="16.2" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="10">
@@ -2303,14 +2336,26 @@
       </c>
       <c r="B17" s="10"/>
       <c r="C17" s="10"/>
-      <c r="D17" s="10"/>
-      <c r="E17" s="10"/>
-      <c r="F17" s="10"/>
-      <c r="G17" s="10"/>
+      <c r="D17" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="E17" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="F17" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="G17" s="10">
+        <v>8</v>
+      </c>
       <c r="H17" s="10"/>
-      <c r="I17" s="10"/>
+      <c r="I17" s="10" t="s">
+        <v>33</v>
+      </c>
       <c r="J17" s="10"/>
-      <c r="K17" s="10"/>
+      <c r="K17" s="10" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="18" spans="1:11" ht="16.2" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="10">
@@ -2375,6 +2420,38 @@
       <c r="I21" s="10"/>
       <c r="J21" s="10"/>
       <c r="K21" s="10"/>
+    </row>
+    <row r="22" spans="1:11" ht="16.2" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="10">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="B22" s="10"/>
+      <c r="C22" s="10"/>
+      <c r="D22" s="10"/>
+      <c r="E22" s="10"/>
+      <c r="F22" s="10"/>
+      <c r="G22" s="10"/>
+      <c r="H22" s="10"/>
+      <c r="I22" s="10"/>
+      <c r="J22" s="10"/>
+      <c r="K22" s="10"/>
+    </row>
+    <row r="23" spans="1:11" ht="16.2" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="10">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="B23" s="10"/>
+      <c r="C23" s="10"/>
+      <c r="D23" s="10"/>
+      <c r="E23" s="10"/>
+      <c r="F23" s="10"/>
+      <c r="G23" s="10"/>
+      <c r="H23" s="10"/>
+      <c r="I23" s="10"/>
+      <c r="J23" s="10"/>
+      <c r="K23" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="8">
